--- a/modules/core/src/main/java/com/jeesite/modules/sys/db/InitCoreData.xlsx
+++ b/modules/core/src/main/java/com/jeesite/modules/sys/db/InitCoreData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="14220" tabRatio="763" activeTab="4"/>
+    <workbookView windowHeight="14340" tabRatio="763" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="5" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15810" uniqueCount="7228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15809" uniqueCount="7228">
   <si>
     <t>configName</t>
   </si>
@@ -27438,9 +27438,7 @@
       <c r="I40" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="K40" s="2" t="s">
-        <v>214</v>
-      </c>
+      <c r="K40" s="2"/>
       <c r="M40" s="2" t="s">
         <v>270</v>
       </c>
